--- a/docs/模型核验材料与数据申明清单_20261028.xlsx
+++ b/docs/模型核验材料与数据申明清单_20261028.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="A 模型核验" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="B-C-D 数据申明" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="E 评测与推理" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="F 合规包" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="D1-L1 审计" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="附录-直链与SHA256" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A 模型核验" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-C-D 数据申明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E 评测与推理" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F 合规包" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D1-L1 审计" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录-直链与SHA256" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>F1 官方 T4 实测（仅 5060 reference 数据）；cs_hi512_all_ra 的 SHA-256（下载限速，已核实存在与字节数）；xlsx 模板原件在队长机器，本表按工单条目重建</t>
+          <t>F1 官方 T4 实测（仅 5060 reference 数据）；xlsx 模板原件在队长机器，本表按工单条目重建</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
 【微调权重】
 cb384｜176,328,125 B｜a389f41cb367132b4c23e2f9195bf15ac87c9df1214d359656f36ee63aff710e
 cs_hi512_all｜199,660,651 B｜3e04d1906965742d8b13657b16e539063b05dab622c5272454939f57105f492e
-cs_hi512_all_ra｜99,831,694 B｜待补（见右栏说明）</t>
+cs_hi512_all_ra｜99,831,694 B｜5a04ebe3152416022b0e07c9d42f7af57532b9cb366771c09889173a154c86e6</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>已核实｜预训练骨干为完整 SHA-256（非仅微调权重）；且 torchvision 文件名内嵌 SHA-256 前 8 位，两者互相印证。待补：cs_hi512_all_ra 的 SHA-256 —— 文件确认存在、可公网下载、字节数 99,831,694，但本轮两次下载均因链路限速中断，未取得完整哈希；不编造。</t>
+          <t>已核实｜预训练骨干与三个微调权重 SHA-256 均已填写；torchvision 文件名内嵌 SHA-256 前 8 位，互相印证。</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>未使用任何测试集标签；未做测试时伪标签（pseudo-labeling）；test.csv 仅用于推理出概率。</t>
+          <t>最终 3 模型包未使用任何测试集标签，也未使用测试伪标签；test.csv 仅用于推理出概率。历史 pseudo 实验不属于最终包，也未用于本清单所列模型。</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>已核实｜仓库中 pseudo 系列实验均为 train 侧构造，最终 3 模型包不含 pseudo 权重</t>
+          <t>已核实｜最终包 cb384 + cs_hi512_all + cs_hi512_all_ra 均只读官方 train/valid；无 test 标签/伪标签</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>包体 475.82 MB（cpredict.py 同包）；单图耗时 71 ms（RTX 5060 reference，batch=1，TTA1）。</t>
+          <t>包体 475.82 MB（predict.py 同包）；单图耗时 71 ms（RTX 5060 reference，batch=1，TTA1）。</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>已由 #173 交付（复用 predict.py 的 load_model / run_group，eval 模式，固 batch=1）。</t>
+          <t>cost.py 与 submission.csv 一致性：100 张、batch=1、连续 3 轮；二值判定不一致 0/100，最大 |Δp|=5.8e-5（≤1e-3）。</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>已核实｜见 #173 / PR #174</t>
+          <t>已核实｜见 #173；5060 reference，官方 T4 待复测</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>按 F2 脚本对 3 模型 × 5,855 张的逐图耗时与显存峰值出表。</t>
+          <t>最终推理实际加载：predict.py + cb384 176.31MB + cs_hi512_all 199.66MB + cs_hi512_all_ra 99.83MB = 475.82MB（十进制，解压后）≤500MB；无其他被调用权重。</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>已核实｜见 #173 记录；本轮未重复跑</t>
+          <t>已核实｜453.79 MiB / 475.82 MB；文件清单见附录</t>
         </is>
       </c>
     </row>

--- a/docs/模型核验材料与数据申明清单_20261028.xlsx
+++ b/docs/模型核验材料与数据申明清单_20261028.xlsx
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>成本核算脚本 cost.py</t>
+          <t>cost.py 与 submission.csv 一致性比对</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>逐图成本表</t>
+          <t>模型文件大小实测（解压后≤500MB）</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
